--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129331604</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129331604</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129331604</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49414-2025 artfynd.xlsx
+++ b/artfynd/A 49414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129331614</v>
       </c>
       <c r="B2" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
